--- a/ConfigExcels/Item.xlsx
+++ b/ConfigExcels/Item.xlsx
@@ -221,7 +221,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -235,10 +235,6 @@
     </font>
     <font>
       <sz val="11.000000"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="12.000000"/>
       <name val="Times New Roman"/>
     </font>
   </fonts>
@@ -289,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -300,14 +296,8 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -331,7 +321,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="baoxin li" id="{3393AA98-60D0-F7B1-8605-DF4E5CD436E6}" userId="baoxin li" providerId="Teamlab"/>
+  <person displayName="baoxin li" id="{77E33A64-D3C0-B696-28AB-D7E7952DB974}" userId="baoxin li" providerId="Teamlab"/>
 </personList>
 </file>
 
@@ -815,25 +805,25 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C1" dT="2026-03-26T06:12:26.27Z" personId="{3393AA98-60D0-F7B1-8605-DF4E5CD436E6}" id="{478F0CFA-DE5C-E7D5-58D5-DE934B6BD88B}" done="0">
+  <threadedComment ref="C1" dT="2026-03-26T06:12:26.27Z" personId="{77E33A64-D3C0-B696-28AB-D7E7952DB974}" id="{478F0CFA-DE5C-E7D5-58D5-DE934B6BD88B}" done="0">
     <text xml:space="preserve">1 = 消耗品
 2 = 材料
 3 = 任务物品
 </text>
   </threadedComment>
-  <threadedComment ref="F1" dT="2026-03-26T06:12:58.98Z" personId="{3393AA98-60D0-F7B1-8605-DF4E5CD436E6}" id="{7D911073-587C-38EB-81A1-AC28A1973EFA}" done="0">
+  <threadedComment ref="F1" dT="2026-03-26T06:12:58.98Z" personId="{77E33A64-D3C0-B696-28AB-D7E7952DB974}" id="{7D911073-587C-38EB-81A1-AC28A1973EFA}" done="0">
     <text xml:space="preserve">1 = 普通
 2 = 优秀
 3 = 稀有
 4 = 史诗
 </text>
   </threadedComment>
-  <threadedComment ref="I1" dT="2026-03-26T06:13:20.68Z" personId="{3393AA98-60D0-F7B1-8605-DF4E5CD436E6}" id="{91B2E812-8C01-BE78-6048-D41CFF1DB55E}" done="0">
+  <threadedComment ref="I1" dT="2026-03-26T06:13:20.68Z" personId="{77E33A64-D3C0-B696-28AB-D7E7952DB974}" id="{91B2E812-8C01-BE78-6048-D41CFF1DB55E}" done="0">
     <text xml:space="preserve">0 = 不可使用
 1 = 可使用
 </text>
   </threadedComment>
-  <threadedComment ref="J1" dT="2026-03-26T06:13:46.46Z" personId="{3393AA98-60D0-F7B1-8605-DF4E5CD436E6}" id="{50F9C3A2-6805-B9E3-D2B1-FE0C19E02763}" done="0">
+  <threadedComment ref="J1" dT="2026-03-26T06:13:46.46Z" personId="{77E33A64-D3C0-B696-28AB-D7E7952DB974}" id="{50F9C3A2-6805-B9E3-D2B1-FE0C19E02763}" done="0">
     <text xml:space="preserve">0 = 无
 1 = 回复HP
 2 = 回复MP
@@ -926,14 +916,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" ht="15">
+    <row r="3" s="0" customFormat="1" ht="15">
       <c r="A3" s="3">
         <v>1001</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
         <v>1</v>
       </c>
       <c r="D3" s="4">
@@ -962,72 +952,72 @@
       </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>1002</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="5">
         <v>1</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <v>20</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <v>12</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <v>1</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="5">
         <v>1</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="5">
         <v>2</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="5">
         <v>30</v>
       </c>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="7">
+      <c r="A5" s="5">
         <v>2001</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="5">
         <v>2</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <v>99</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="5">
         <v>5</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <v>1</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="5">
         <v>0</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="5">
         <v>0</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="5">
         <v>0</v>
       </c>
     </row>

--- a/ConfigExcels/Item.xlsx
+++ b/ConfigExcels/Item.xlsx
@@ -18,13 +18,40 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={F99ECA39-4E56-A671-A18B-B702AC6DFB78}</author>
     <author>tc={478F0CFA-DE5C-E7D5-58D5-DE934B6BD88B}</author>
     <author>tc={7D911073-587C-38EB-81A1-AC28A1973EFA}</author>
     <author>tc={91B2E812-8C01-BE78-6048-D41CFF1DB55E}</author>
     <author>tc={50F9C3A2-6805-B9E3-D2B1-FE0C19E02763}</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" xr:uid="{478F0CFA-DE5C-E7D5-58D5-DE934B6BD88B}">
+    <comment ref="M1" authorId="0" xr:uid="{F99ECA39-4E56-A671-A18B-B702AC6DFB78}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">baoxin li:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+1 = 剑
+2 = 头
+3 = 甲
+4 = 手
+5 = 腿
+6 = 饰品
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="1" xr:uid="{478F0CFA-DE5C-E7D5-58D5-DE934B6BD88B}">
       <text>
         <r>
           <rPr>
@@ -43,11 +70,12 @@
 1 = 消耗品
 2 = 材料
 3 = 任务物品
+4 = 装备
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="1" xr:uid="{7D911073-587C-38EB-81A1-AC28A1973EFA}">
+    <comment ref="F1" authorId="2" xr:uid="{7D911073-587C-38EB-81A1-AC28A1973EFA}">
       <text>
         <r>
           <rPr>
@@ -71,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="2" xr:uid="{91B2E812-8C01-BE78-6048-D41CFF1DB55E}">
+    <comment ref="I1" authorId="3" xr:uid="{91B2E812-8C01-BE78-6048-D41CFF1DB55E}">
       <text>
         <r>
           <rPr>
@@ -93,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="3" xr:uid="{50F9C3A2-6805-B9E3-D2B1-FE0C19E02763}">
+    <comment ref="J1" authorId="4" xr:uid="{50F9C3A2-6805-B9E3-D2B1-FE0C19E02763}">
       <text>
         <r>
           <rPr>
@@ -122,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>道具ID</t>
   </si>
@@ -136,7 +164,7 @@
     <t>最大堆叠数量</t>
   </si>
   <si>
-    <t>售价</t>
+    <t>出售价钱</t>
   </si>
   <si>
     <t>品质</t>
@@ -157,6 +185,36 @@
     <t>使用效果值</t>
   </si>
   <si>
+    <t>是否可装备</t>
+  </si>
+  <si>
+    <t>装备类型</t>
+  </si>
+  <si>
+    <t>力量</t>
+  </si>
+  <si>
+    <t>敏捷</t>
+  </si>
+  <si>
+    <t>智力</t>
+  </si>
+  <si>
+    <t>防御力</t>
+  </si>
+  <si>
+    <t>最大HP</t>
+  </si>
+  <si>
+    <t>最大MP</t>
+  </si>
+  <si>
+    <t>暴击率</t>
+  </si>
+  <si>
+    <t>暴击伤害</t>
+  </si>
+  <si>
     <t>ItemId</t>
   </si>
   <si>
@@ -190,6 +248,36 @@
     <t>UseEffectValue</t>
   </si>
   <si>
+    <t>CanEquip</t>
+  </si>
+  <si>
+    <t>EquipSlotType</t>
+  </si>
+  <si>
+    <t>AddStrength</t>
+  </si>
+  <si>
+    <t>AddAgility</t>
+  </si>
+  <si>
+    <t>AddIntelligence</t>
+  </si>
+  <si>
+    <t>AddDefense</t>
+  </si>
+  <si>
+    <t>AddMaxHp</t>
+  </si>
+  <si>
+    <t>AddMaxMp</t>
+  </si>
+  <si>
+    <t>AddCritRate</t>
+  </si>
+  <si>
+    <t>AddCritDamage</t>
+  </si>
+  <si>
     <t>小型生命药水</t>
   </si>
   <si>
@@ -215,13 +303,175 @@
   </si>
   <si>
     <t>普通材料</t>
+  </si>
+  <si>
+    <t>普通的剑</t>
+  </si>
+  <si>
+    <t>Icons/Items/Sword1</t>
+  </si>
+  <si>
+    <t>这是一个普通的剑</t>
+  </si>
+  <si>
+    <t>上好的剑</t>
+  </si>
+  <si>
+    <t>Icons/Items/Sword2</t>
+  </si>
+  <si>
+    <t>这是一个上好的剑</t>
+  </si>
+  <si>
+    <t>传奇的剑</t>
+  </si>
+  <si>
+    <t>Icons/Items/Sword3</t>
+  </si>
+  <si>
+    <t>这是一个传奇的剑</t>
+  </si>
+  <si>
+    <t>普通的头</t>
+  </si>
+  <si>
+    <t>Icons/Items/Helmet1</t>
+  </si>
+  <si>
+    <t>这是一个普通的头</t>
+  </si>
+  <si>
+    <t>上好的头</t>
+  </si>
+  <si>
+    <t>Icons/Items/Helmet2</t>
+  </si>
+  <si>
+    <t>这是一个上好的头</t>
+  </si>
+  <si>
+    <t>传奇的头</t>
+  </si>
+  <si>
+    <t>Icons/Items/Helmet3</t>
+  </si>
+  <si>
+    <t>这是一个传奇的头</t>
+  </si>
+  <si>
+    <t>普通的甲</t>
+  </si>
+  <si>
+    <t>Icons/Items/Armor1</t>
+  </si>
+  <si>
+    <t>这是一个普通的甲</t>
+  </si>
+  <si>
+    <t>上好的甲</t>
+  </si>
+  <si>
+    <t>Icons/Items/Armor2</t>
+  </si>
+  <si>
+    <t>这是一个上好的甲</t>
+  </si>
+  <si>
+    <t>传奇的甲</t>
+  </si>
+  <si>
+    <t>Icons/Items/Armor3</t>
+  </si>
+  <si>
+    <t>这是一个传奇的甲</t>
+  </si>
+  <si>
+    <t>普通的手</t>
+  </si>
+  <si>
+    <t>Icons/Items/Gauntlets1</t>
+  </si>
+  <si>
+    <t>这是一个普通的手</t>
+  </si>
+  <si>
+    <t>上好的手</t>
+  </si>
+  <si>
+    <t>Icons/Items/Gauntlets2</t>
+  </si>
+  <si>
+    <t>这是一个上好的手</t>
+  </si>
+  <si>
+    <t>传奇的手</t>
+  </si>
+  <si>
+    <t>Icons/Items/Gauntlets3</t>
+  </si>
+  <si>
+    <t>这是一个传奇的手</t>
+  </si>
+  <si>
+    <t>普通的腿</t>
+  </si>
+  <si>
+    <t>Icons/Items/LegArmor1</t>
+  </si>
+  <si>
+    <t>这是一个普通的腿</t>
+  </si>
+  <si>
+    <t>上好的腿</t>
+  </si>
+  <si>
+    <t>Icons/Items/LegArmor2</t>
+  </si>
+  <si>
+    <t>这是一个上好的腿</t>
+  </si>
+  <si>
+    <t>传奇的腿</t>
+  </si>
+  <si>
+    <t>Icons/Items/LegArmor3</t>
+  </si>
+  <si>
+    <t>这是一个传奇的腿</t>
+  </si>
+  <si>
+    <t>普通的饰品</t>
+  </si>
+  <si>
+    <t>Icons/Items/Accessories1</t>
+  </si>
+  <si>
+    <t>这是一个普通的饰品</t>
+  </si>
+  <si>
+    <t>上好的饰品</t>
+  </si>
+  <si>
+    <t>Icons/Items/Accessories2</t>
+  </si>
+  <si>
+    <t>这是一个上好的饰品</t>
+  </si>
+  <si>
+    <t>传奇的饰品</t>
+  </si>
+  <si>
+    <t>Icons/Items/Accessories3</t>
+  </si>
+  <si>
+    <t>这是一个传奇的饰品</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -234,7 +484,18 @@
       <name val="Times New Roman"/>
     </font>
     <font>
+      <b/>
       <sz val="11.000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="12.000000"/>
       <name val="Times New Roman"/>
     </font>
   </fonts>
@@ -285,19 +546,31 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="2" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf fontId="4" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -321,7 +594,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="baoxin li" id="{77E33A64-D3C0-B696-28AB-D7E7952DB974}" userId="baoxin li" providerId="Teamlab"/>
+  <person displayName="baoxin li" id="{107A3185-5886-CC13-E95B-C88A34CC9CB3}" userId="baoxin li" providerId="Teamlab"/>
 </personList>
 </file>
 
@@ -805,25 +1078,35 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C1" dT="2026-03-26T06:12:26.27Z" personId="{77E33A64-D3C0-B696-28AB-D7E7952DB974}" id="{478F0CFA-DE5C-E7D5-58D5-DE934B6BD88B}" done="0">
+  <threadedComment ref="M1" dT="2026-04-06T02:22:50.42Z" personId="{107A3185-5886-CC13-E95B-C88A34CC9CB3}" id="{F99ECA39-4E56-A671-A18B-B702AC6DFB78}" done="0">
+    <text xml:space="preserve">1 = 剑
+2 = 头
+3 = 甲
+4 = 手
+5 = 腿
+6 = 饰品
+</text>
+  </threadedComment>
+  <threadedComment ref="C1" dT="2026-03-26T06:12:26.27Z" personId="{107A3185-5886-CC13-E95B-C88A34CC9CB3}" id="{478F0CFA-DE5C-E7D5-58D5-DE934B6BD88B}" done="0">
     <text xml:space="preserve">1 = 消耗品
 2 = 材料
 3 = 任务物品
+4 = 装备
 </text>
   </threadedComment>
-  <threadedComment ref="F1" dT="2026-03-26T06:12:58.98Z" personId="{77E33A64-D3C0-B696-28AB-D7E7952DB974}" id="{7D911073-587C-38EB-81A1-AC28A1973EFA}" done="0">
+  <threadedComment ref="F1" dT="2026-03-26T06:12:58.98Z" personId="{107A3185-5886-CC13-E95B-C88A34CC9CB3}" id="{7D911073-587C-38EB-81A1-AC28A1973EFA}" done="0">
     <text xml:space="preserve">1 = 普通
 2 = 优秀
 3 = 稀有
 4 = 史诗
 </text>
   </threadedComment>
-  <threadedComment ref="I1" dT="2026-03-26T06:13:20.68Z" personId="{77E33A64-D3C0-B696-28AB-D7E7952DB974}" id="{91B2E812-8C01-BE78-6048-D41CFF1DB55E}" done="0">
+  <threadedComment ref="I1" dT="2026-03-26T06:13:20.68Z" personId="{107A3185-5886-CC13-E95B-C88A34CC9CB3}" id="{91B2E812-8C01-BE78-6048-D41CFF1DB55E}" done="0">
     <text xml:space="preserve">0 = 不可使用
 1 = 可使用
 </text>
   </threadedComment>
-  <threadedComment ref="J1" dT="2026-03-26T06:13:46.46Z" personId="{77E33A64-D3C0-B696-28AB-D7E7952DB974}" id="{50F9C3A2-6805-B9E3-D2B1-FE0C19E02763}" done="0">
+  <threadedComment ref="J1" dT="2026-03-26T06:13:46.46Z" personId="{107A3185-5886-CC13-E95B-C88A34CC9CB3}" id="{50F9C3A2-6805-B9E3-D2B1-FE0C19E02763}" done="0">
     <text xml:space="preserve">0 = 无
 1 = 回复HP
 2 = 回复MP
@@ -844,181 +1127,1503 @@
     <col customWidth="1" min="8" max="8" width="29.57421875"/>
     <col customWidth="1" min="9" max="10" width="14.8515625"/>
     <col customWidth="1" min="11" max="11" width="15.7109375"/>
+    <col customWidth="1" min="12" max="21" style="1" width="12.7109375"/>
+    <col customWidth="1" min="22" max="22" width="12.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" ht="30">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="2" t="s">
+    <row r="2" ht="15">
+      <c r="A2" s="4" t="s">
         <v>21</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" s="0" customFormat="1" ht="15">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>1001</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="B3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="7">
+        <v>1</v>
+      </c>
+      <c r="D3" s="7">
         <v>20</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="7">
         <v>10</v>
       </c>
-      <c r="F3" s="4">
-        <v>1</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="4">
-        <v>1</v>
-      </c>
-      <c r="J3" s="4">
-        <v>1</v>
-      </c>
-      <c r="K3" s="4">
+      <c r="F3" s="7">
+        <v>1</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="7">
+        <v>1</v>
+      </c>
+      <c r="J3" s="7">
+        <v>1</v>
+      </c>
+      <c r="K3" s="7">
         <v>50</v>
+      </c>
+      <c r="L3" s="8">
+        <v>0</v>
+      </c>
+      <c r="M3" s="8">
+        <v>0</v>
+      </c>
+      <c r="N3" s="8">
+        <v>0</v>
+      </c>
+      <c r="O3" s="8">
+        <v>0</v>
+      </c>
+      <c r="P3" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>0</v>
+      </c>
+      <c r="R3" s="8">
+        <v>0</v>
+      </c>
+      <c r="S3" s="8">
+        <v>0</v>
+      </c>
+      <c r="T3" s="8">
+        <v>0</v>
+      </c>
+      <c r="U3" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="4">
+      <c r="A4" s="7">
         <v>1002</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="5">
-        <v>1</v>
-      </c>
-      <c r="D4" s="5">
+      <c r="B4" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1</v>
+      </c>
+      <c r="D4" s="8">
         <v>20</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="8">
         <v>12</v>
       </c>
-      <c r="F4" s="5">
-        <v>1</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
+      <c r="F4" s="8">
+        <v>1</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" s="8">
+        <v>1</v>
+      </c>
+      <c r="J4" s="8">
         <v>2</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="8">
         <v>30</v>
+      </c>
+      <c r="L4" s="8">
+        <v>0</v>
+      </c>
+      <c r="M4" s="8">
+        <v>0</v>
+      </c>
+      <c r="N4" s="8">
+        <v>0</v>
+      </c>
+      <c r="O4" s="8">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
+        <v>0</v>
+      </c>
+      <c r="S4" s="8">
+        <v>0</v>
+      </c>
+      <c r="T4" s="8">
+        <v>0</v>
+      </c>
+      <c r="U4" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="5">
+      <c r="A5" s="8">
         <v>2001</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="5">
+      <c r="B5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="8">
         <v>2</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="8">
         <v>99</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="8">
         <v>5</v>
       </c>
-      <c r="F5" s="5">
-        <v>1</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="F5" s="8">
+        <v>1</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="8">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8">
+        <v>0</v>
+      </c>
+      <c r="K5" s="8">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8">
+        <v>0</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0</v>
+      </c>
+      <c r="N5" s="8">
+        <v>0</v>
+      </c>
+      <c r="O5" s="8">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8">
+        <v>0</v>
+      </c>
+      <c r="S5" s="8">
+        <v>0</v>
+      </c>
+      <c r="T5" s="8">
+        <v>0</v>
+      </c>
+      <c r="U5" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6" s="8">
+        <v>3001</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="8">
+        <v>4</v>
+      </c>
+      <c r="D6" s="8">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8">
+        <v>50</v>
+      </c>
+      <c r="F6" s="8">
+        <v>2</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" s="8">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8">
+        <v>0</v>
+      </c>
+      <c r="K6" s="8">
+        <v>0</v>
+      </c>
+      <c r="L6" s="8">
+        <v>1</v>
+      </c>
+      <c r="M6" s="8">
+        <v>1</v>
+      </c>
+      <c r="N6" s="8">
+        <v>5</v>
+      </c>
+      <c r="O6" s="8">
+        <v>0</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8">
+        <v>0</v>
+      </c>
+      <c r="S6" s="8">
+        <v>0</v>
+      </c>
+      <c r="T6" s="8">
+        <v>0</v>
+      </c>
+      <c r="U6" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" s="8">
+        <v>3002</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="8">
+        <v>4</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8">
+        <v>150</v>
+      </c>
+      <c r="F7" s="8">
+        <v>3</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" s="8">
+        <v>0</v>
+      </c>
+      <c r="J7" s="8">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8">
+        <v>1</v>
+      </c>
+      <c r="M7" s="8">
+        <v>1</v>
+      </c>
+      <c r="N7" s="8">
+        <v>15</v>
+      </c>
+      <c r="O7" s="8">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="8">
+        <v>0</v>
+      </c>
+      <c r="S7" s="8">
+        <v>0</v>
+      </c>
+      <c r="T7" s="8">
+        <v>0</v>
+      </c>
+      <c r="U7" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" s="8">
+        <v>3003</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="8">
+        <v>4</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8">
+        <v>300</v>
+      </c>
+      <c r="F8" s="8">
+        <v>4</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8" s="8">
+        <v>0</v>
+      </c>
+      <c r="J8" s="8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="8">
+        <v>0</v>
+      </c>
+      <c r="L8" s="8">
+        <v>1</v>
+      </c>
+      <c r="M8" s="8">
+        <v>1</v>
+      </c>
+      <c r="N8" s="8">
         <v>30</v>
       </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
+      <c r="O8" s="8">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8">
+        <v>0</v>
+      </c>
+      <c r="S8" s="8">
+        <v>0</v>
+      </c>
+      <c r="T8" s="8">
+        <v>0</v>
+      </c>
+      <c r="U8" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" s="8">
+        <v>3004</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="8">
+        <v>4</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1</v>
+      </c>
+      <c r="E9" s="8">
+        <v>50</v>
+      </c>
+      <c r="F9" s="8">
+        <v>2</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" s="8">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8">
+        <v>0</v>
+      </c>
+      <c r="K9" s="8">
+        <v>0</v>
+      </c>
+      <c r="L9" s="8">
+        <v>1</v>
+      </c>
+      <c r="M9" s="8">
+        <v>2</v>
+      </c>
+      <c r="N9" s="8">
+        <v>0</v>
+      </c>
+      <c r="O9" s="8">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>5</v>
+      </c>
+      <c r="R9" s="8">
+        <v>50</v>
+      </c>
+      <c r="S9" s="8">
+        <v>0</v>
+      </c>
+      <c r="T9" s="8">
+        <v>0</v>
+      </c>
+      <c r="U9" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="8">
+        <v>3005</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="8">
+        <v>4</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8">
+        <v>150</v>
+      </c>
+      <c r="F10" s="8">
+        <v>3</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" s="8">
+        <v>0</v>
+      </c>
+      <c r="J10" s="8">
+        <v>0</v>
+      </c>
+      <c r="K10" s="8">
+        <v>0</v>
+      </c>
+      <c r="L10" s="8">
+        <v>1</v>
+      </c>
+      <c r="M10" s="8">
+        <v>2</v>
+      </c>
+      <c r="N10" s="8">
+        <v>0</v>
+      </c>
+      <c r="O10" s="8">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>15</v>
+      </c>
+      <c r="R10" s="8">
+        <v>80</v>
+      </c>
+      <c r="S10" s="8">
+        <v>0</v>
+      </c>
+      <c r="T10" s="8">
+        <v>0</v>
+      </c>
+      <c r="U10" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" s="8">
+        <v>3006</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="8">
+        <v>4</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8">
+        <v>300</v>
+      </c>
+      <c r="F11" s="8">
+        <v>4</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" s="8">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8">
+        <v>1</v>
+      </c>
+      <c r="M11" s="8">
+        <v>2</v>
+      </c>
+      <c r="N11" s="8">
+        <v>0</v>
+      </c>
+      <c r="O11" s="8">
+        <v>0</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>30</v>
+      </c>
+      <c r="R11" s="8">
+        <v>150</v>
+      </c>
+      <c r="S11" s="8">
+        <v>0</v>
+      </c>
+      <c r="T11" s="8">
+        <v>0</v>
+      </c>
+      <c r="U11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" s="8">
+        <v>3007</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="8">
+        <v>4</v>
+      </c>
+      <c r="D12" s="8">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8">
+        <v>50</v>
+      </c>
+      <c r="F12" s="8">
+        <v>2</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12" s="8">
+        <v>0</v>
+      </c>
+      <c r="J12" s="8">
+        <v>0</v>
+      </c>
+      <c r="K12" s="8">
+        <v>0</v>
+      </c>
+      <c r="L12" s="8">
+        <v>1</v>
+      </c>
+      <c r="M12" s="8">
+        <v>3</v>
+      </c>
+      <c r="N12" s="8">
+        <v>0</v>
+      </c>
+      <c r="O12" s="8">
+        <v>0</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>5</v>
+      </c>
+      <c r="R12" s="8">
+        <v>50</v>
+      </c>
+      <c r="S12" s="8">
+        <v>0</v>
+      </c>
+      <c r="T12" s="8">
+        <v>0</v>
+      </c>
+      <c r="U12" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" s="8">
+        <v>3008</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="8">
+        <v>4</v>
+      </c>
+      <c r="D13" s="8">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8">
+        <v>150</v>
+      </c>
+      <c r="F13" s="8">
+        <v>3</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I13" s="8">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8">
+        <v>1</v>
+      </c>
+      <c r="M13" s="8">
+        <v>3</v>
+      </c>
+      <c r="N13" s="8">
+        <v>0</v>
+      </c>
+      <c r="O13" s="8">
+        <v>0</v>
+      </c>
+      <c r="P13" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>15</v>
+      </c>
+      <c r="R13" s="8">
+        <v>80</v>
+      </c>
+      <c r="S13" s="8">
+        <v>0</v>
+      </c>
+      <c r="T13" s="8">
+        <v>0</v>
+      </c>
+      <c r="U13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" s="8">
+        <v>3009</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="8">
+        <v>4</v>
+      </c>
+      <c r="D14" s="8">
+        <v>1</v>
+      </c>
+      <c r="E14" s="8">
+        <v>300</v>
+      </c>
+      <c r="F14" s="8">
+        <v>4</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="I14" s="8">
+        <v>0</v>
+      </c>
+      <c r="J14" s="8">
+        <v>0</v>
+      </c>
+      <c r="K14" s="8">
+        <v>0</v>
+      </c>
+      <c r="L14" s="8">
+        <v>1</v>
+      </c>
+      <c r="M14" s="8">
+        <v>3</v>
+      </c>
+      <c r="N14" s="8">
+        <v>0</v>
+      </c>
+      <c r="O14" s="8">
+        <v>0</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>30</v>
+      </c>
+      <c r="R14" s="8">
+        <v>150</v>
+      </c>
+      <c r="S14" s="8">
+        <v>0</v>
+      </c>
+      <c r="T14" s="8">
+        <v>0</v>
+      </c>
+      <c r="U14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" s="8">
+        <v>3010</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="8">
+        <v>4</v>
+      </c>
+      <c r="D15" s="8">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8">
+        <v>50</v>
+      </c>
+      <c r="F15" s="8">
+        <v>2</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I15" s="8">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8">
+        <v>1</v>
+      </c>
+      <c r="M15" s="8">
+        <v>4</v>
+      </c>
+      <c r="N15" s="8">
+        <v>0</v>
+      </c>
+      <c r="O15" s="8">
+        <v>0</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>5</v>
+      </c>
+      <c r="R15" s="8">
+        <v>50</v>
+      </c>
+      <c r="S15" s="8">
+        <v>0</v>
+      </c>
+      <c r="T15" s="8">
+        <v>0</v>
+      </c>
+      <c r="U15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16" s="8">
+        <v>3011</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="8">
+        <v>4</v>
+      </c>
+      <c r="D16" s="8">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8">
+        <v>150</v>
+      </c>
+      <c r="F16" s="8">
+        <v>3</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I16" s="8">
+        <v>0</v>
+      </c>
+      <c r="J16" s="8">
+        <v>0</v>
+      </c>
+      <c r="K16" s="8">
+        <v>0</v>
+      </c>
+      <c r="L16" s="8">
+        <v>1</v>
+      </c>
+      <c r="M16" s="8">
+        <v>4</v>
+      </c>
+      <c r="N16" s="8">
+        <v>0</v>
+      </c>
+      <c r="O16" s="8">
+        <v>0</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>15</v>
+      </c>
+      <c r="R16" s="8">
+        <v>80</v>
+      </c>
+      <c r="S16" s="8">
+        <v>0</v>
+      </c>
+      <c r="T16" s="8">
+        <v>0</v>
+      </c>
+      <c r="U16" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" s="8">
+        <v>3012</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="8">
+        <v>4</v>
+      </c>
+      <c r="D17" s="8">
+        <v>1</v>
+      </c>
+      <c r="E17" s="8">
+        <v>300</v>
+      </c>
+      <c r="F17" s="8">
+        <v>4</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
+        <v>1</v>
+      </c>
+      <c r="M17" s="8">
+        <v>4</v>
+      </c>
+      <c r="N17" s="8">
+        <v>0</v>
+      </c>
+      <c r="O17" s="8">
+        <v>0</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>30</v>
+      </c>
+      <c r="R17" s="8">
+        <v>150</v>
+      </c>
+      <c r="S17" s="8">
+        <v>0</v>
+      </c>
+      <c r="T17" s="8">
+        <v>0</v>
+      </c>
+      <c r="U17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" s="8">
+        <v>3013</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="8">
+        <v>4</v>
+      </c>
+      <c r="D18" s="8">
+        <v>1</v>
+      </c>
+      <c r="E18" s="8">
+        <v>50</v>
+      </c>
+      <c r="F18" s="8">
+        <v>2</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I18" s="8">
+        <v>0</v>
+      </c>
+      <c r="J18" s="8">
+        <v>0</v>
+      </c>
+      <c r="K18" s="8">
+        <v>0</v>
+      </c>
+      <c r="L18" s="8">
+        <v>1</v>
+      </c>
+      <c r="M18" s="8">
+        <v>5</v>
+      </c>
+      <c r="N18" s="8">
+        <v>0</v>
+      </c>
+      <c r="O18" s="8">
+        <v>0</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>5</v>
+      </c>
+      <c r="R18" s="8">
+        <v>50</v>
+      </c>
+      <c r="S18" s="8">
+        <v>0</v>
+      </c>
+      <c r="T18" s="8">
+        <v>0</v>
+      </c>
+      <c r="U18" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19" s="8">
+        <v>3014</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="8">
+        <v>4</v>
+      </c>
+      <c r="D19" s="8">
+        <v>1</v>
+      </c>
+      <c r="E19" s="8">
+        <v>150</v>
+      </c>
+      <c r="F19" s="8">
+        <v>3</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="I19" s="8">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8">
+        <v>1</v>
+      </c>
+      <c r="M19" s="8">
+        <v>5</v>
+      </c>
+      <c r="N19" s="8">
+        <v>0</v>
+      </c>
+      <c r="O19" s="8">
+        <v>0</v>
+      </c>
+      <c r="P19" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>15</v>
+      </c>
+      <c r="R19" s="8">
+        <v>80</v>
+      </c>
+      <c r="S19" s="8">
+        <v>0</v>
+      </c>
+      <c r="T19" s="8">
+        <v>0</v>
+      </c>
+      <c r="U19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20" s="8">
+        <v>3015</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="8">
+        <v>4</v>
+      </c>
+      <c r="D20" s="8">
+        <v>1</v>
+      </c>
+      <c r="E20" s="8">
+        <v>300</v>
+      </c>
+      <c r="F20" s="8">
+        <v>4</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I20" s="8">
+        <v>0</v>
+      </c>
+      <c r="J20" s="8">
+        <v>0</v>
+      </c>
+      <c r="K20" s="8">
+        <v>0</v>
+      </c>
+      <c r="L20" s="8">
+        <v>1</v>
+      </c>
+      <c r="M20" s="8">
+        <v>5</v>
+      </c>
+      <c r="N20" s="8">
+        <v>0</v>
+      </c>
+      <c r="O20" s="8">
+        <v>0</v>
+      </c>
+      <c r="P20" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="8">
+        <v>30</v>
+      </c>
+      <c r="R20" s="8">
+        <v>150</v>
+      </c>
+      <c r="S20" s="8">
+        <v>0</v>
+      </c>
+      <c r="T20" s="8">
+        <v>0</v>
+      </c>
+      <c r="U20" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21" s="8">
+        <v>3016</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="8">
+        <v>4</v>
+      </c>
+      <c r="D21" s="8">
+        <v>1</v>
+      </c>
+      <c r="E21" s="8">
+        <v>50</v>
+      </c>
+      <c r="F21" s="8">
+        <v>2</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="I21" s="8">
+        <v>0</v>
+      </c>
+      <c r="J21" s="8">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8">
+        <v>0</v>
+      </c>
+      <c r="L21" s="8">
+        <v>1</v>
+      </c>
+      <c r="M21" s="8">
+        <v>6</v>
+      </c>
+      <c r="N21" s="8">
+        <v>0</v>
+      </c>
+      <c r="O21" s="8">
+        <v>0</v>
+      </c>
+      <c r="P21" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>0</v>
+      </c>
+      <c r="R21" s="8">
+        <v>0</v>
+      </c>
+      <c r="S21" s="8">
+        <v>10</v>
+      </c>
+      <c r="T21" s="8">
+        <v>5</v>
+      </c>
+      <c r="U21" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="A22" s="8">
+        <v>3017</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="8">
+        <v>4</v>
+      </c>
+      <c r="D22" s="8">
+        <v>1</v>
+      </c>
+      <c r="E22" s="8">
+        <v>150</v>
+      </c>
+      <c r="F22" s="8">
+        <v>3</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="I22" s="8">
+        <v>0</v>
+      </c>
+      <c r="J22" s="8">
+        <v>0</v>
+      </c>
+      <c r="K22" s="8">
+        <v>0</v>
+      </c>
+      <c r="L22" s="8">
+        <v>1</v>
+      </c>
+      <c r="M22" s="8">
+        <v>6</v>
+      </c>
+      <c r="N22" s="8">
+        <v>0</v>
+      </c>
+      <c r="O22" s="8">
+        <v>0</v>
+      </c>
+      <c r="P22" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>0</v>
+      </c>
+      <c r="R22" s="8">
+        <v>0</v>
+      </c>
+      <c r="S22" s="8">
+        <v>25</v>
+      </c>
+      <c r="T22" s="8">
+        <v>10</v>
+      </c>
+      <c r="U22" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" s="8">
+        <v>3018</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23" s="8">
+        <v>4</v>
+      </c>
+      <c r="D23" s="8">
+        <v>1</v>
+      </c>
+      <c r="E23" s="8">
+        <v>300</v>
+      </c>
+      <c r="F23" s="8">
+        <v>4</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="I23" s="8">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8">
+        <v>0</v>
+      </c>
+      <c r="K23" s="8">
+        <v>0</v>
+      </c>
+      <c r="L23" s="8">
+        <v>1</v>
+      </c>
+      <c r="M23" s="8">
+        <v>6</v>
+      </c>
+      <c r="N23" s="8">
+        <v>0</v>
+      </c>
+      <c r="O23" s="8">
+        <v>0</v>
+      </c>
+      <c r="P23" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>0</v>
+      </c>
+      <c r="R23" s="8">
+        <v>0</v>
+      </c>
+      <c r="S23" s="8">
+        <v>50</v>
+      </c>
+      <c r="T23" s="8">
+        <v>20</v>
+      </c>
+      <c r="U23" s="8">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
